--- a/hardware/BOM.xlsx
+++ b/hardware/BOM.xlsx
@@ -4965,7 +4965,7 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>mates J10 - pick header+socket pair</t>
+          <t>Mates MAIN J10 (female socket PM254V-12-16-H85 / C46595985). Header+socket pair confirmed 2026-08-02: 8.5mm+2.5mm insulation = 11.00mm board gap, 6.0mm mating pin inside socket 3.68-6.35mm window. See README_PCBWAY.md assembly notes.</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr"/>
@@ -5248,39 +5248,35 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Suntsu SSWFS-S01 (TAP/BYP)</t>
+          <t>Alpha SF12011F-0102-20R-M-011 (momentary, TAP/BYP + TAP/TEMPO)</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>SSWFS-S01</t>
+          <t>SF12011F-0102-M</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>SSWFS-S01-AC09-HWH (PC-pin) or Amplified Parts P-H604 equivalent</t>
+          <t>SF12011F-0102-20R-M-011</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>DIGI-KEY</t>
+          <t>PCBWay (turnkey, sourced by MPN)</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>CUSTOMER SUPPLIED</t>
+          <t>N/A - Alpha (Taiwan) direct, not LCSC/DK stocked</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>DO NOT SOURCE - no fab-side distributor stocks this class of part (Digi-Key Marketplace only; Mouser none; JLCPCB has no foot-switch category). Commodity pedal part: Love My Switches PCB-mount \.99, Amplified Parts P-H604 dimensions match (12mm x 1mm bushing, 14.3 long, body 25.3 x 12.6). Fitted by Jason at final assembly. PC-pin variant chosen 2026-08-02 - no board cutouts needed.</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>DNP</t>
-        </is>
-      </c>
+          <t>2026-09-05: switched from Suntsu SSWFS-S01 (unsourceable) to Alpha SF12011F-0102-20R-M-011. Both SW1 and SW2 kept MOMENTARY (not latching) to preserve the STARVE gesture (both-held) and existing 2-switch/5-gesture firmware in stomps.c - a latching bypass switch was considered and rejected. "011F" prefix = Alpha's genuine PCB-mount (PC-pin) terminal type per their SF12 series datasheet, confirmed board-mountable with no panel cutouts (matches project's existing no-cutout architecture) - the E-Switch FS5700 alternate looked into earlier was rejected because it uses rear solder lugs, not PCB pins, and cannot be machine-assembled. VERIFIED from Alpha's own SF12 series datasheet (user-supplied PDF, page 3, SF12011F-0102-20R-M-011 outline drawing): terminals in a straight row, 2.5mm pitch, ~1.0mm pin width; pinout Pin 1=N.O., Pin 2=COM, Pin 3=N.C. (wiring diagram: PUSH 1-2 ON, FREE 2-3 ON). Pin 1 (N.O.) wired to GND, pin 2 (COM) wired to the existing GPIO/pullup net, pin 3 (N.C.) left genuinely unconnected. Thread M12x0.75 vs prior M12x1.0 spec - panel hole stays D12.2 (M12 nominal OD unaffected by thread pitch), no enclosure change needed. Body 13.4mm dia, ~12mm deep below panel - fits existing 15.0+/-1.0mm enclosure depth budget. Since the real part's pin pitch/positions differ from the old SSWFS-S01 footprint, the PCB routing at SW1/SW2 was re-run (new footprint, corrected pinout, existing traces rerouted to reach the new pad positions) - DRC and ERC both clean (0 errors) as of 2026-09-05. No longer DNP - PCBWay turnkey should be able to source and place this by MPN.</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">

--- a/hardware/BOM.xlsx
+++ b/hardware/BOM.xlsx
@@ -679,7 +679,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>CP_Elec_10x10.2</t>
+          <t>CP_Elec_10x10</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>CP_Elec_8x10.2</t>
+          <t>CP_Elec_8x10</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>C107,C108</t>
+          <t>C108,C112</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>X7R/C0G per value; &gt;=25V on VA nets, 50V for C104</t>
+          <t>MP1584 output bulk pair, 2 x 22uF in parallel on +5V. 2026-09-11: this row used to say C107,C108 - C107 was a DUPLICATE refdes (mcu sheet already had a 100n C107 on FREQ_CV) so this cap had no footprint on the board at all. Renamed to C112 and placed at (62.6, 25.0) on the PCB. X7R/X5R, &gt;=25V.</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr"/>

--- a/hardware/BOM.xlsx
+++ b/hardware/BOM.xlsx
@@ -929,11 +929,11 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>C101,C106,C107,C111,C121,C122,C123,C124,C20,C21,C22,C23,C30,C31,C33,C34,C35,C40,C49,C50,C63,C64,C65,C66,C67,C70,C71,C73,C76,C77,C78,C83,C84,C85,C91,C910,C911,C93,C94,C95,C96,C97,C98,C99</t>
+          <t>C101,C106,C107,C111,C121,C122,C123,C124,C125,C20,C21,C22,C23,C30,C31,C33,C34,C35,C40,C49,C50,C63,C64,C65,C66,C67,C70,C71,C73,C76,C77,C78,C83,C84,C85,C91,C910,C911,C93,C94,C95,C96,C97,C98,C99</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -3181,11 +3181,11 @@
         <v>61</v>
       </c>
       <c r="B62" s="3" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>R106A,R107A,R110,R111,R112A,R113A,R117A,R121A,R125A,R142,R145,R146,R147,R148,R161,R162,R163,R164,R165,R166,R167,R168,R169,R171,R172,R174,R25,R33,R35,R48,R49,R51,R64,R68,R76,R79,R83,R88,R90,R92</t>
+          <t>R106A,R107A,R110,R111,R112A,R113A,R117A,R121A,R125A,R142,R145,R146,R147,R148,R161,R162,R163,R164,R165,R166,R167,R168,R169,R171,R172,R174,R175,R25,R33,R35,R48,R49,R51,R64,R68,R76,R79,R83,R88,R90,R92</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
@@ -5239,16 +5239,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>SW1,SW2</t>
+          <t>SW1,SW2,SW3</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Alpha SF12011F-0102-20R-M-011 (momentary, TAP/BYP + TAP/TEMPO)</t>
+          <t>Alpha SF12011F-0102-20R-M-011 (momentary, stomps A/B/C)</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -5273,7 +5273,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05: switched from Suntsu SSWFS-S01 (unsourceable) to Alpha SF12011F-0102-20R-M-011. Both SW1 and SW2 kept MOMENTARY (not latching) to preserve the STARVE gesture (both-held) and existing 2-switch/5-gesture firmware in stomps.c - a latching bypass switch was considered and rejected. "011F" prefix = Alpha's genuine PCB-mount (PC-pin) terminal type per their SF12 series datasheet, confirmed board-mountable with no panel cutouts (matches project's existing no-cutout architecture) - the E-Switch FS5700 alternate looked into earlier was rejected because it uses rear solder lugs, not PCB pins, and cannot be machine-assembled. VERIFIED from Alpha's own SF12 series datasheet (user-supplied PDF, page 3, SF12011F-0102-20R-M-011 outline drawing): terminals in a straight row, 2.5mm pitch, ~1.0mm pin width; pinout Pin 1=N.O., Pin 2=COM, Pin 3=N.C. (wiring diagram: PUSH 1-2 ON, FREE 2-3 ON). Pin 1 (N.O.) wired to GND, pin 2 (COM) wired to the existing GPIO/pullup net, pin 3 (N.C.) left genuinely unconnected. Thread M12x0.75 vs prior M12x1.0 spec - panel hole stays D12.2 (M12 nominal OD unaffected by thread pitch), no enclosure change needed. Body 13.4mm dia, ~12mm deep below panel - fits existing 15.0+/-1.0mm enclosure depth budget. Since the real part's pin pitch/positions differ from the old SSWFS-S01 footprint, the PCB routing at SW1/SW2 was re-run (new footprint, corrected pinout, existing traces rerouted to reach the new pad positions) - DRC and ERC both clean (0 errors) as of 2026-09-05. No longer DNP - PCBWay turnkey should be able to source and place this by MPN.</t>
+          <t>2026-09-05: switched from Suntsu SSWFS-S01 (unsourceable) to Alpha SF12011F-0102-20R-M-011. Both SW1 and SW2 kept MOMENTARY (not latching) to preserve the STARVE gesture (both-held) and existing 2-switch/5-gesture firmware in stomps.c - a latching bypass switch was considered and rejected. "011F" prefix = Alpha's genuine PCB-mount (PC-pin) terminal type per their SF12 series datasheet, confirmed board-mountable with no panel cutouts (matches project's existing no-cutout architecture) - the E-Switch FS5700 alternate looked into earlier was rejected because it uses rear solder lugs, not PCB pins, and cannot be machine-assembled. VERIFIED from Alpha's own SF12 series datasheet (user-supplied PDF, page 3, SF12011F-0102-20R-M-011 outline drawing): terminals in a straight row, 2.5mm pitch, ~1.0mm pin width; pinout Pin 1=N.O., Pin 2=COM, Pin 3=N.C. (wiring diagram: PUSH 1-2 ON, FREE 2-3 ON). Pin 1 (N.O.) wired to GND, pin 2 (COM) wired to the existing GPIO/pullup net, pin 3 (N.C.) left genuinely unconnected. Thread M12x0.75 vs prior M12x1.0 spec - panel hole stays D12.2 (M12 nominal OD unaffected by thread pitch), no enclosure change needed. Body 13.4mm dia, ~12mm deep below panel - fits existing 15.0+/-1.0mm enclosure depth budget. Since the real part's pin pitch/positions differ from the old SSWFS-S01 footprint, the PCB routing at SW1/SW2 was re-run (new footprint, corrected pinout, existing traces rerouted to reach the new pad positions) - DRC and ERC both clean (0 errors) as of 2026-09-05. No longer DNP - PCBWay turnkey should be able to source and place this by MPN. | Rev8 2026-09-21: third stomp SW3 added at board centre x=69.00, SW1/SW2 moved outboard to 23.28/114.72 (1.800in pitch), same part/wiring (pin1 N.O.-&gt;GND, pin2 COM-&gt;STOMP3 via J1 pin 15 -&gt; GP22).</t>
         </is>
       </c>
       <c r="J11" s="3" t="n"/>
@@ -5407,21 +5407,21 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Stomps: Suntsu SSWFS-S01-AC09-HWH via Digi-Key (PCBWay buys from DK/Mouser for turnkey).</t>
+          <t>Stomps: 3x Alpha SF12011F-0102-20R-M-011 (SW1,SW2,SW3) - Alpha Taiwan direct, PCBWay turnkey sources by MPN (not LCSC/DK stocked). Rev8 2026-09-21 added SW3.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  CONFIRM at order time that PCBWay will purchase Digi-Key MARKETPLACE items; if not, use SSWFS-S01-AC05-HWH (DK own stock,</t>
+          <t xml:space="preserve">  (Suntsu SSWFS-S01 references are obsolete - superseded 2026-09-05 by the Alpha part above.)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  solder lug) shipped loose + 2 wires per stomp to the same control-board pads.</t>
+          <t xml:space="preserve">  Stomp wiring: pin 1 (N.O.) to GND, pin 2 (COM) to STOMP net, pin 3 (N.C.) unconnected.</t>
         </is>
       </c>
     </row>
